--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,7 +291,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}pa-panel-01:At least one activity component must be present {component.exists()}pa-agg-01:When moderateActivity or vigorousActivity are present, aggregateActivity SHOULD equal moderateActivity (or 0) + (vigorousActivity × 2, or 0) {(component.where(code.coding.where(code = '77592-4').exists()).exists()
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}pa-panel-01:At least one activity component must be present {component.exists()}pa-agg-01:When moderateActivity or vigorousActivity are present, aggregateActivity SHOULD equal moderateActivity (or 0) + (vigorousActivity × 2, or 0) {(component.where(code.coding.where(code = '77592-4').exists()).exists()
  or component.where(code.coding.where(code = '77593-2').exists()).exists())
 implies
 component.where(code.coding.where(code = '101691-4').exists()).value.ofType(Quantity).value =
@@ -1138,7 +1138,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -1615,7 +1615,7 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
+    <t>Reason why no clinically or analytically meaningful component result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
@@ -6228,7 +6228,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>350</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -9238,7 +9238,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>501</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -11176,7 +11176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>571</v>
       </c>
@@ -11195,7 +11195,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -13114,7 +13114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>589</v>
       </c>
@@ -13133,7 +13133,7 @@
         <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
@@ -15052,7 +15052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>606</v>
       </c>
@@ -15071,7 +15071,7 @@
         <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>21</v>
@@ -16144,7 +16144,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>618</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>93</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$133</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4539" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5156" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,16 +87,36 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation profile for recording physical activity duration as a panel
-(moderate, vigorous, aggregate components) derived from either a wearable device or
-the EHIS-PAQ/ATHIS questionnaire (Q7/PE7). Supports four valid component combinations:
-  (a) aggregate only           — questionnaire source (Q7/PE7 → aggregateActivity)
-  (b) moderate only            — manual source; vigorous implicitly 0,
-                                 aggregate = moderateActivity (pa-agg-01 warning
-                                 if aggregateActivity absent)
-  (c) moderate + aggregate     — partial wearable or manual source
-  (d) vigorous + aggregate     — partial wearable source
-  (e) all three                — full wearable source. </t>
+    <t>Observation profile for recording physical activity duration as a panel
+(moderate, vigorous, and two alternative aggregate components) derived from either a
+wearable device or the EHIS-PAQ/ATHIS questionnaire (Q7/PE7).
+Two aggregate flavors may be sent independently of each other:
+  - aggregateActivity          — plain/unweighted total: moderateActivity (or 0) +
+                                  vigorousActivity (or 0). Also used standalone when
+                                  moderate/vigorous cannot be distinguished at all
+                                  (e.g. a single questionnaire total). See pa-agg-02.
+  - aggregateActivityWeighted  — WHO/IPAQ moderate-equivalent total: moderateActivity
+                                  (or 0) + (vigorousActivity × 2, or 0). See pa-agg-01.
+Both, either, or neither aggregate MAY be present; pa-panel-01 only requires that at
+least one component (of any kind) exists. Sending only an aggregate (without
+moderateActivity/vigorousActivity) is valid and expected whenever the source cannot
+distinguish intensity levels at all (e.g. a single questionnaire total). However,
+whenever a source CAN distinguish moderate from vigorous activity, it SHOULD send
+moderateActivity and vigorousActivity individually (in addition to any aggregate) —
+sending only a pre-computed aggregate discards information a consumer might need.
+This cannot be enforced by an invariant (an instance cannot express "the source
+could have distinguished this but chose not to"), so it is stated here as
+implementation guidance rather than a machine-checkable rule.
+Example component combinations (not exhaustive):
+  (a) aggregateActivity only              — questionnaire source, no intensity split (Q7/PE7)
+  (b) moderate only                       — manual source; vigorous implicitly 0,
+                                             aggregates SHOULD equal moderateActivity
+                                             (pa-agg-01/pa-agg-02 warning if absent)
+  (c) moderate + aggregateActivityWeighted — partial wearable or manual source
+  (d) vigorous + aggregateActivityWeighted — partial wearable source
+  (e) moderate + vigorous + aggregateActivityWeighted            — full wearable source
+  (g) moderate + vigorous + aggregateActivity + aggregateActivityWeighted — full wearable
+      source reporting both aggregate flavors side by side</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -291,16 +311,25 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}pa-panel-01:At least one activity component must be present {component.exists()}pa-agg-01:When moderateActivity or vigorousActivity are present, aggregateActivity SHOULD equal moderateActivity (or 0) + (vigorousActivity × 2, or 0) {(component.where(code.coding.where(code = '77592-4').exists()).exists()
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}pa-panel-01:At least one activity component must be present {component.exists()}pa-agg-01:When moderateActivity or vigorousActivity are present, aggregateActivityWeighted SHOULD equal moderateActivity (or 0) + (vigorousActivity × 2, or 0) {(component.where(code.coding.where(code = '77592-4').exists()).exists()
+ or component.where(code.coding.where(code = '77593-2').exists()).exists())
+implies
+component.where(code.coding.where(code = '68130003').exists()).value.ofType(Quantity).value =
+  iif(component.where(code.coding.where(code = '77592-4').exists()).exists(),
+      component.where(code.coding.where(code = '77592-4').exists()).value.ofType(Quantity).value,
+      0)
+  + (iif(component.where(code.coding.where(code = '77593-2').exists()).exists(),
+         component.where(code.coding.where(code = '77593-2').exists()).value.ofType(Quantity).value,
+         0) * 2)}pa-agg-02:When moderateActivity or vigorousActivity are present, aggregateActivity SHOULD equal moderateActivity (or 0) + vigorousActivity (or 0), with no intensity weighting {(component.where(code.coding.where(code = '77592-4').exists()).exists()
  or component.where(code.coding.where(code = '77593-2').exists()).exists())
 implies
 component.where(code.coding.where(code = '101691-4').exists()).value.ofType(Quantity).value =
   iif(component.where(code.coding.where(code = '77592-4').exists()).exists(),
       component.where(code.coding.where(code = '77592-4').exists()).value.ofType(Quantity).value,
       0)
-  + (iif(component.where(code.coding.where(code = '77593-2').exists()).exists(),
-         component.where(code.coding.where(code = '77593-2').exists()).value.ofType(Quantity).value,
-         0) * 2)}pa-wearable-01:When method is Automated, aggregateActivity must be present {method.coding.exists(system = 'http://snomed.info/sct' and code = '8359006') implies component.where(code.coding.where(code = '101691-4').exists()).exists()}pa-manual-comp-01:When method is Manual, classificationMethod component must be absent or carry only code self-rp {method.coding.exists(system = 'http://snomed.info/sct' and code = '87982008')
+  + iif(component.where(code.coding.where(code = '77593-2').exists()).exists(),
+        component.where(code.coding.where(code = '77593-2').exists()).value.ofType(Quantity).value,
+        0)}pa-wearable-01:When method is Automated, aggregateActivityWeighted must be present {method.coding.exists(system = 'http://snomed.info/sct' and code = '8359006') implies component.where(code.coding.where(code = '68130003').exists()).exists()}pa-manual-comp-01:When method is Manual, classificationMethod component must be absent or carry only code self-rp {method.coding.exists(system = 'http://snomed.info/sct' and code = '87982008')
 implies (
   component.where(code.coding.where(code = '246501002').exists()).empty()
   or component.where(code.coding.where(code = '246501002').exists())
@@ -1556,7 +1585,7 @@
     <t>Physical activity duration components</t>
   </si>
   <si>
-    <t>Panel components: moderateActivity, vigorousActivity, aggregateActivity (min/wk) and classificationMethod (CodeableConcept).</t>
+    <t>Panel components: moderateActivity, vigorousActivity, aggregateActivity (unweighted, min/wk), aggregateActivityWeighted (WHO/IPAQ weighted, min/wk) and classificationMethod (CodeableConcept).</t>
   </si>
   <si>
     <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1950,6 +1979,66 @@
   </si>
   <si>
     <t>Observation.component:aggregateActivity.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted</t>
+  </si>
+  <si>
+    <t>aggregateActivityWeighted</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.id</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="68130003"/&gt;
+    &lt;display value="Physical activity"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].value</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].comparator</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].unit</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].system</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.value[x].code</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:aggregateActivityWeighted.referenceRange</t>
   </si>
   <si>
     <t>Observation.component:classificationMethod</t>
@@ -2316,12 +2405,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP117"/>
+  <dimension ref="A1:AP133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.7578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.54296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.95703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.44921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -15418,7 +15507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
         <v>609</v>
       </c>
@@ -15439,7 +15528,7 @@
         <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>21</v>
@@ -16052,7 +16141,7 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>182</v>
+        <v>519</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>498</v>
@@ -16089,11 +16178,13 @@
         <v>21</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y114" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z114" t="s" s="2">
-        <v>617</v>
+        <v>21</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>21</v>
@@ -16144,12 +16235,12 @@
         <v>349</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16163,7 +16254,7 @@
         <v>93</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>21</v>
@@ -16172,20 +16263,16 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>502</v>
+        <v>161</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>21</v>
       </c>
@@ -16209,13 +16296,13 @@
         <v>21</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>21</v>
@@ -16233,7 +16320,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>501</v>
+        <v>163</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16242,10 +16329,10 @@
         <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>21</v>
@@ -16254,10 +16341,10 @@
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>21</v>
@@ -16268,14 +16355,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>360</v>
+        <v>138</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -16294,20 +16381,18 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>361</v>
+        <v>140</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -16331,31 +16416,31 @@
         <v>21</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>505</v>
+        <v>170</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16367,33 +16452,33 @@
         <v>21</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16404,7 +16489,7 @@
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>21</v>
@@ -16413,22 +16498,22 @@
         <v>21</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>419</v>
+        <v>529</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16477,13 +16562,13 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>21</v>
@@ -16498,20 +16583,1962 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q118" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="R118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN117" t="s" s="2">
+      <c r="AN124" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AO117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP117" t="s" s="2">
+      <c r="AO124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y130" s="2"/>
+      <c r="Z130" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP133" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP117">
+  <autoFilter ref="A1:AP133">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16521,7 +18548,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI116">
+  <conditionalFormatting sqref="A2:AI132">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
